--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -12,6 +12,8 @@
     <sheet name="Detalle 73 lineas" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Alertas datos" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Para buscar en eBay" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resumen por categoria" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Clasificacion Savvy" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -733,8 +735,6 @@
       <c r="J3" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -773,8 +773,6 @@
       <c r="J4" t="n">
         <v>7.22</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -909,8 +907,6 @@
       <c r="J7" t="n">
         <v>4.27</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -949,8 +945,6 @@
       <c r="J8" t="n">
         <v>2.11</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -989,8 +983,6 @@
       <c r="J9" t="n">
         <v>1.93</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1029,8 +1021,6 @@
       <c r="J10" t="n">
         <v>1.81</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1069,8 +1059,6 @@
       <c r="J11" t="n">
         <v>1.76</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1109,8 +1097,6 @@
       <c r="J12" t="n">
         <v>1.57</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1149,8 +1135,6 @@
       <c r="J13" t="n">
         <v>1.56</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1189,8 +1173,6 @@
       <c r="J14" t="n">
         <v>1.52</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1229,8 +1211,6 @@
       <c r="J15" t="n">
         <v>1.48</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1269,8 +1249,6 @@
       <c r="J16" t="n">
         <v>1.34</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1309,8 +1287,6 @@
       <c r="J17" t="n">
         <v>1.07</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1349,8 +1325,6 @@
       <c r="J18" t="n">
         <v>0.97</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1389,8 +1363,6 @@
       <c r="J19" t="n">
         <v>0.77</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1429,8 +1401,6 @@
       <c r="J20" t="n">
         <v>0.68</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1469,8 +1439,6 @@
       <c r="J21" t="n">
         <v>0.49</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1509,8 +1477,6 @@
       <c r="J22" t="n">
         <v>0.49</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1549,8 +1515,6 @@
       <c r="J23" t="n">
         <v>0.46</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1589,8 +1553,6 @@
       <c r="J24" t="n">
         <v>0.32</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1629,8 +1591,6 @@
       <c r="J25" t="n">
         <v>0.27</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1669,8 +1629,6 @@
       <c r="J26" t="n">
         <v>0.22</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1709,8 +1667,6 @@
       <c r="J27" t="n">
         <v>0.21</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1749,8 +1705,6 @@
       <c r="J28" t="n">
         <v>0.18</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1789,8 +1743,6 @@
       <c r="J29" t="n">
         <v>0.15</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1829,8 +1781,6 @@
       <c r="J30" t="n">
         <v>0.12</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1869,8 +1819,6 @@
       <c r="J31" t="n">
         <v>0.1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1909,8 +1857,6 @@
       <c r="J32" t="n">
         <v>0.08</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1949,8 +1895,6 @@
       <c r="J33" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1989,8 +1933,6 @@
       <c r="J34" t="n">
         <v>0.05</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2029,8 +1971,6 @@
       <c r="J35" t="n">
         <v>0.04</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2069,8 +2009,6 @@
       <c r="J36" t="n">
         <v>0.04</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2109,8 +2047,6 @@
       <c r="J37" t="n">
         <v>0.03</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2149,8 +2085,6 @@
       <c r="J38" t="n">
         <v>0.03</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2189,8 +2123,6 @@
       <c r="J39" t="n">
         <v>0.03</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2229,8 +2161,6 @@
       <c r="J40" t="n">
         <v>0.02</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2269,8 +2199,6 @@
       <c r="J41" t="n">
         <v>0.02</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2309,8 +2237,6 @@
       <c r="J42" t="n">
         <v>0.02</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2349,8 +2275,6 @@
       <c r="J43" t="n">
         <v>0.02</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2389,8 +2313,6 @@
       <c r="J44" t="n">
         <v>0.02</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2429,8 +2351,6 @@
       <c r="J45" t="n">
         <v>0.02</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2623,7 +2543,6 @@
           <t>0060258355017</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
@@ -2675,7 +2594,6 @@
           <t>0060258352146</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
@@ -2727,7 +2645,6 @@
           <t>0060258355017</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
@@ -2779,7 +2696,6 @@
           <t>0060258355031</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
@@ -2831,7 +2747,6 @@
           <t>0060258360899</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
@@ -2883,7 +2798,6 @@
           <t>0060258360936</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
@@ -2935,7 +2849,6 @@
           <t>0060258363098</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
@@ -2987,7 +2900,6 @@
           <t>0060258363104</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
@@ -3039,7 +2951,6 @@
           <t>0060258364170</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
@@ -3091,7 +3002,6 @@
           <t>0060258364590</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
@@ -3143,7 +3053,6 @@
           <t>0060258365252</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
@@ -3195,7 +3104,6 @@
           <t>0060258508031</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Brita Hub Filter 6/1ct SIOC</t>
@@ -3247,7 +3155,6 @@
           <t>0060258508031</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>BRITA HUB FILTER 6/1CT SIOC</t>
@@ -3299,7 +3206,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
@@ -3351,7 +3257,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
@@ -3403,7 +3308,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
@@ -3567,7 +3471,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
@@ -3619,7 +3522,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
@@ -3671,7 +3573,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
@@ -3723,7 +3624,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
@@ -3775,7 +3675,6 @@
           <t>0060258509670</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
@@ -3827,7 +3726,6 @@
           <t>0060258355031</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Brita Pitcher Filters 24/3ct Shipper</t>
@@ -3879,7 +3777,6 @@
           <t>0060258360899</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Brita SOHO Pitcher White 2/1ct</t>
@@ -3931,7 +3828,6 @@
           <t>0060258362435</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Brita Elite 12/1ct Sidekick Display</t>
@@ -3983,7 +3879,6 @@
           <t>0060258362619</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
@@ -4035,7 +3930,6 @@
           <t>0060258363128</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
@@ -4087,7 +3981,6 @@
           <t>0060258363159</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
@@ -4139,7 +4032,6 @@
           <t>0060258364552</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
@@ -4191,7 +4083,6 @@
           <t>0060258364606</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
@@ -4243,7 +4134,6 @@
           <t>0060258364668</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
@@ -4295,7 +4185,6 @@
           <t>0060258365245</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
@@ -4347,7 +4236,6 @@
           <t>0060258506884</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
@@ -4399,7 +4287,6 @@
           <t>0060258509847</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
@@ -4451,7 +4338,6 @@
           <t>0060258509854</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
@@ -5175,7 +5061,6 @@
           <t>0060258509670</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
@@ -5227,7 +5112,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Brita Advanced Pitcher Filter 10/10ct Value Pallet PK07</t>
@@ -5279,7 +5163,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Brita Advanced Pitcher Filter 10/10ct Value Pallet PK07</t>
@@ -5331,7 +5214,6 @@
           <t>0060258355031</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Brita Pitcher Filters 24/3ct Shipper</t>
@@ -5383,7 +5265,6 @@
           <t>0060258364545</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
@@ -5435,7 +5316,6 @@
           <t>0060258364552</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
@@ -5487,7 +5367,6 @@
           <t>0060258364606</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
@@ -5539,7 +5418,6 @@
           <t>0060258356182</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
@@ -5591,7 +5469,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Brita Advanced Pitcher Filter 10/10ct Value Pallet PK07</t>
@@ -5643,7 +5520,6 @@
           <t>0060258360899</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Brita SOHO Pitcher White 2/1ct</t>
@@ -5695,7 +5571,6 @@
           <t>0060258364606</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
@@ -5803,7 +5678,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Brita Advanced Pitcher Filter 10/10ct Value Pallet PK07</t>
@@ -5855,7 +5729,6 @@
           <t>0060258509670</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
@@ -5907,7 +5780,6 @@
           <t>0060258507263</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
@@ -5959,7 +5831,6 @@
           <t>0060258507263</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
@@ -6011,7 +5882,6 @@
           <t>0060258507928</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
@@ -6175,7 +6045,6 @@
           <t>0060258356182</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
@@ -6227,7 +6096,6 @@
           <t>0060258509670</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
@@ -6391,7 +6259,6 @@
           <t>0060258359916</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Brita Advanced Pitcher Filter 10/10ct Value Pallet PK07</t>
@@ -7429,4 +7296,2152 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UPCs</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>% costo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44185.15144</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1198</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16198.0989</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>623</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6339.34384</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1174.415</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>136</v>
+      </c>
+      <c r="D6" t="n">
+        <v>745.8240000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>84</v>
+      </c>
+      <c r="D7" t="n">
+        <v>597.839959</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" t="n">
+        <v>205.028</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SI - poco volumen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Consumible</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Costo_total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>% del costo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32707.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5589.168000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258362435</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>432</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2967.552</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258508031</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1219.53144</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>136</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>745.8240000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>109</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>674.564</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="H8" t="n">
+        <v>532.64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>473.632</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>103.004</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SI - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>68.01600000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SI - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H12" t="n">
+        <v>34.008</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20.864</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>524</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5013.632000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F15" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4503.755200000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>283</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3334.872</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>98</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1462.552</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>96</v>
+      </c>
+      <c r="F18" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1342.5696</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>93</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1259.592</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>93</v>
+      </c>
+      <c r="F20" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1093.1871</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>88</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1084.5648</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NO - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>96</v>
+      </c>
+      <c r="F22" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1053.6672</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>96</v>
+      </c>
+      <c r="F23" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1030.4448</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>144</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H24" t="n">
+        <v>929.88</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>52</v>
+      </c>
+      <c r="F25" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="H25" t="n">
+        <v>341.7968</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>48</v>
+      </c>
+      <c r="F26" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H26" t="n">
+        <v>338.496</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="H27" t="n">
+        <v>321.792</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H28" t="n">
+        <v>219.8912</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>28</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="H29" t="n">
+        <v>190.7976</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="G30" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>149.5188</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>23</v>
+      </c>
+      <c r="F31" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H31" t="n">
+        <v>148.601</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>18</v>
+      </c>
+      <c r="F32" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H32" t="n">
+        <v>125.496</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H33" t="n">
+        <v>83.664</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="H34" t="n">
+        <v>54.65584</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>50.183959</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>29.008</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H37" t="n">
+        <v>27.4864</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="G38" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>23.6816</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="H39" t="n">
+        <v>20.944</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G40" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13.7432</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="G41" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12.8043</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="G42" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.8043</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="G44" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H44" t="n">
+        <v>11.552</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="H45" t="n">
+        <v>11.464</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -14,6 +14,9 @@
     <sheet name="Para buscar en eBay" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Resumen por categoria" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Clasificacion Savvy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Canal MARKETPLACE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Canal PALLET" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Notas y escenarios" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +34,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,8 +68,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -565,6 +584,165 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Comision eBay asumida</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13.25% del precio de venta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Envio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Estimado por categoria. Pitchers y dispensers pagan peso dimensional (caja grande, poco peso).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Breakeven eBay</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(Costo + Envio) / (1 - 0.1325). Debajo de ese precio pierdes dinero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BE % del MSRP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Breakeven como % del MSRP. Arriba de 100% = imposible vender por unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regla MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20+ unidades Y breakeven &lt;= 95% del MSRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regla PALLET</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&lt;=10 unidades, o &lt;20 unidades, o breakeven &gt; 95% del MSRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESCENARIOS (solo los 13 SKUs de marketplace)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vender a 85% del MSRP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>neto $10,134 sobre costo $53,225 = ROI 19% (solo 7 de 13 SKUs rentables)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vender a 100% del MSRP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>neto $27,378 = ROI 51% (13 de 13 rentables)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Vender a 115% del MSRP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>neto $44,623 = ROI 84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Precios reales de eBay. Faltan por bloqueo de red; estos numeros son estimados.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9444,4 +9622,2208 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Envio est.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Breakeven eBay</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BE % del MSRP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Neto/und @85%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ROI @85%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>524</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="I3" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>140</v>
+      </c>
+      <c r="E4" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258362435</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>432</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>98</v>
+      </c>
+      <c r="E6" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="I6" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="I7" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>93</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="I8" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>060258508031</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>156</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>136</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I10" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>109</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="I11" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="F12" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="I13" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Envio est.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Breakeven eBay</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BE % del MSRP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Neto/und @85%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ROI @85%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>-97</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>283</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>93</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="I4" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>-39</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>88</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="I5" t="n">
+        <v>124</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-10.16</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>-82</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="I7" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>-51</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>144</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-8.84</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>-137</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>52</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>-132</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>-29</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I11" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="I12" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>-126</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="F13" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="I13" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-8.83</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>-137</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="I15" t="n">
+        <v>99</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="I16" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PALLET - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="I17" t="n">
+        <v>99</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="I18" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PALLET - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="I19" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="I20" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="I21" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="I22" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-7.76</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>-54</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I23" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="I24" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="I25" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>-49</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="I26" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I27" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="I28" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>-76</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="I29" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>-76</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>-138</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="I31" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-10.25</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>-89</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="I32" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>-73</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -17,6 +17,8 @@
     <sheet name="Canal MARKETPLACE" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Canal PALLET" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Notas y escenarios" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Lotes pallet" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Pallet detalle" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,7 +683,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -725,7 +726,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -736,6 +736,1322 @@
         <is>
           <t>Precios reales de eBay. Faltan por bloqueo de red; estos numeros son estimados.</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SKUs</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Venta @50% retail</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Utilidad</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Costo/und</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A - Filtros sueltos 1ct</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5589.168000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13972.92</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6986.46</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1397.29</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>792</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7974.6455</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19661.41</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9830.700000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1856.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C - Botellas</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D4" t="n">
+        <v>597.839959</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1491.54</v>
+      </c>
+      <c r="F4" t="n">
+        <v>745.77</v>
+      </c>
+      <c r="G4" t="n">
+        <v>147.93</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" t="n">
+        <v>179</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2059.21144</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5045.29</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2522.64</v>
+      </c>
+      <c r="G5" t="n">
+        <v>463.43</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A - Filtros sueltos 1ct</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5589.168000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>283</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3334.872</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1093.1871</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1053.6672</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>96</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1030.4448</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>144</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>929.88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="H8" t="n">
+        <v>341.7968</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B - Pitchers de volumen</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="H9" t="n">
+        <v>190.7976</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C - Botellas</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>338.496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C - Botellas</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H11" t="n">
+        <v>125.496</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C - Botellas</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H12" t="n">
+        <v>83.664</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C - Botellas</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50.183959</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>88</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1084.5648</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H15" t="n">
+        <v>219.8912</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>149.5188</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H17" t="n">
+        <v>148.601</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>103.004</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H19" t="n">
+        <v>68.01600000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="H20" t="n">
+        <v>54.65584</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H21" t="n">
+        <v>34.008</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>29.008</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G23" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>27.4864</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23.6816</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20.944</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="H26" t="n">
+        <v>20.864</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13.7432</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="G28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12.8043</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12.8043</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="G31" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H31" t="n">
+        <v>11.552</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>D - Mixto / cola larga</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="H32" t="n">
+        <v>11.464</v>
       </c>
     </row>
   </sheetData>

--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -19,6 +19,8 @@
     <sheet name="Notas y escenarios" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Lotes pallet" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Pallet detalle" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Precios eBay" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="eBay escenarios" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +42,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +59,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,11 +77,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2059,6 +2067,2996 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Envio est.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Breakeven eBay</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>eBay piso</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>eBay promedio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>avg/MSRP %</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Precio conserv.</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Neto conserv.</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ROI conserv. %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>listados</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confianza</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Sospecha multipack</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre en eBay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="K2" t="n">
+        <v>93</v>
+      </c>
+      <c r="L2" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="N2" t="n">
+        <v>43</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Brita Pitcher Replacement Filters #987554 Value Pack Brand New</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="K3" t="n">
+        <v>233</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="O3" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>NEW Brita Standard Replacement Carbon Water Filter Model OB03 Pitcher Dispenser</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>524</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="I4" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="K4" t="n">
+        <v>275</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Brita Elite Faucet Mount Water Filter System Chrome | Removes 99% of Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>283</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="H5" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="I5" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>154</v>
+      </c>
+      <c r="L5" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Brita Water Filter System Original 10 Cup Capacity Pitcher + 1 Filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258362435</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>432</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>143</v>
+      </c>
+      <c r="L6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>39</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Elite BPA-Free Water Filter Replacement - Reduces 99% Lead, Lasts 120 Gallons</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="H7" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="I7" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>103</v>
+      </c>
+      <c r="L7" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Brita Large 10 Cup Pacifica White Water Filter Pitcher With Filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>93</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="I8" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="K8" t="n">
+        <v>120</v>
+      </c>
+      <c r="L8" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="N8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NEW Brita Chrome Tap Water Faucet Filtration System with 2 EXTRA Filters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>144</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>255</v>
+      </c>
+      <c r="L9" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-105</v>
+      </c>
+      <c r="O9" t="n">
+        <v>13</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Metro Water Filter Pitcher with SmartLight Change Indicator, BPA-Free, Replaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>136</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="I10" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="K10" t="n">
+        <v>162</v>
+      </c>
+      <c r="L10" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N10" t="n">
+        <v>17</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Brita Water Bottle Replacement Filters, BPA-Free, Replaces 1,800 Plastic Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>109</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="I11" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="K11" t="n">
+        <v>175</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10 cup Water Filter Brand New Sealed W 9 Filters</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="H12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I12" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="K12" t="n">
+        <v>101</v>
+      </c>
+      <c r="L12" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>53</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>BRITA Standard Pitcher Replacement Filter - Works in all BRITA Sys Except Stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="K13" t="n">
+        <v>141</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>61</v>
+      </c>
+      <c r="O13" t="n">
+        <v>18</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Filter Replacements for Water Pitchers and Dispensers 2 Count Blue Plastic</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>52</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="H14" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="K14" t="n">
+        <v>204</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>-6.53</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-99</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Brita Original Water Filter Pitcher 6-Cup with 1 Filter New</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="I15" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85</v>
+      </c>
+      <c r="L15" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10-Cup Water Filter Pitcher + 1 Elite Filter BPA Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="K16" t="n">
+        <v>150</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-6.77</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-105</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Brita Soho 5 Cup Pitcher With Filter BPA Free Water Filtration System NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="H17" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="I17" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="J17" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="K17" t="n">
+        <v>130</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="N17" t="n">
+        <v>53</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Brita Water Filter for Brita Faucet Filtration Systems - Chrome Silver 2 Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="I18" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="J18" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K18" t="n">
+        <v>303</v>
+      </c>
+      <c r="L18" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N18" t="n">
+        <v>11</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>BRITA FR-200 Faucet Mount Replacement Filter, Lead Removal, Chrome, 1 Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="I19" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="K19" t="n">
+        <v>156</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="N19" t="n">
+        <v>51</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Brita Faucet Mount Water Filter System Multi-Use Tap Water Filter for Kitchens</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="H20" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K20" t="n">
+        <v>147</v>
+      </c>
+      <c r="L20" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11</v>
+      </c>
+      <c r="O20" t="n">
+        <v>14</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3 NEW Brita Faucet System Replacement Water Filter Cartridge CHROME FR-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="I21" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="K21" t="n">
+        <v>117</v>
+      </c>
+      <c r="L21" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N21" t="n">
+        <v>59</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Brita standard replacement  Water Filter for Pitchers 6 Count - Sealed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="J22" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="K22" t="n">
+        <v>219</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-40</v>
+      </c>
+      <c r="O22" t="n">
+        <v>20</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Brita On Tap Faucet Filtration System -NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="J23" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="K23" t="n">
+        <v>156</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR - tipo no coincide</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>BRITA Premium Leak Proof Filtered Water Bottle • 26 Oz 768ml NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="H24" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="I24" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>159</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR - tipo no coincide</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Premium Stainless Steel Leak Proof Filtered Insulated Water Bottle Brita 20 oz</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>20</v>
+      </c>
+      <c r="G25" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="J25" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="K25" t="n">
+        <v>71</v>
+      </c>
+      <c r="L25" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>-12.14</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-84</v>
+      </c>
+      <c r="O25" t="n">
+        <v>6</v>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR - tipo no coincide</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRAND NEW Brita Elite 10-Cup Water Pitcher </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>96</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="K26" t="n">
+        <v>110</v>
+      </c>
+      <c r="L26" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR - pocos listados</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Brita Large 10 Cup White Tahoe Water Filter Pitcher with 1 Standard Filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E27" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="H27" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="I27" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="J27" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="K27" t="n">
+        <v>40</v>
+      </c>
+      <c r="L27" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>-18.94</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-59</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Brita Water Filter 6 Cup Denali Water Pitcher Dispenser with Elite Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>98</v>
+      </c>
+      <c r="E28" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="I28" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="J28" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="K28" t="n">
+        <v>164</v>
+      </c>
+      <c r="L28" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N28" t="n">
+        <v>23</v>
+      </c>
+      <c r="O28" t="n">
+        <v>10</v>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Brita Wave Elite 10 Cup Smart Water Filter System Pitcher w two filters NEW OB53</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>060258508031</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>156</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="H29" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="I29" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="J29" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="K29" t="n">
+        <v>210</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N29" t="n">
+        <v>46</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Brita Hub Replacement Water Filter, BPA-Free, Replaces 900 1 Count, White</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>48</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="H30" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="J30" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="K30" t="n">
+        <v>168</v>
+      </c>
+      <c r="L30" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Brita 36 oz Water Filter Bottle BPA Free with Straw Leakproof Convenient Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14</v>
+      </c>
+      <c r="G31" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="I31" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="J31" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-74.44</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-100</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="H32" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="I32" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="J32" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="K32" t="n">
+        <v>263</v>
+      </c>
+      <c r="L32" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>SI - avg inflado</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Brita Hard-Sided Plastic Premium Filtering Water Bottle, 36 Ounces, Orchid</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="H33" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="I33" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="J33" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K33" t="n">
+        <v>49</v>
+      </c>
+      <c r="L33" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>-13.42</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-98</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="H34" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="I34" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="J34" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="K34" t="n">
+        <v>53</v>
+      </c>
+      <c r="L34" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>-18.48</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-144</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="H35" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="I35" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="J35" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="K35" t="n">
+        <v>57</v>
+      </c>
+      <c r="L35" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>-17.23</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-149</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>93</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="J36" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="L36" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>88</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F37" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="J37" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="L37" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-51</v>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>96</v>
+      </c>
+      <c r="E38" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="F38" t="n">
+        <v>14</v>
+      </c>
+      <c r="G38" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="J38" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="L38" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>16</v>
+      </c>
+      <c r="E39" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="F39" t="n">
+        <v>14</v>
+      </c>
+      <c r="G39" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>-27.74</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-202</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>HUGE Lot of 16 Brita Pitcher Replacement Water Filters Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>28</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="J40" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="L40" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-94</v>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J41" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="L41" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N41" t="n">
+        <v>10</v>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="F42" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="L42" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="N42" t="n">
+        <v>27</v>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="J43" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="L43" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-17</v>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="J44" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="L44" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-45</v>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14</v>
+      </c>
+      <c r="G45" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="L45" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-105</v>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Universo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Los 21 UPCs de confianza ALTA = $56,675 = 81.6% del costo de la carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Si vendes al PISO (igualando al mas barato)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>neto -$9,404  = ROI -17%  | solo 8 de 21 SKUs rentables</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Si vendes al PROMEDIO de eBay</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>neto +$62,249 = ROI 110% | 20 de 21 rentables  (OJO: promedio inflado por multipacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Si vendes CONSERVADOR (tope = MSRP)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>neto +$12,981 = ROI 23%  | 14 de 21 rentables</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Por que el promedio esta inflado</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>En 10 SKUs el promedio de eBay supera 150% del MSRP. Eso pasa cuando listados de multipack se cuelan en el promedio de un producto de 1 unidad. No asumas ese precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cual usar</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>El CONSERVADOR. Es el unico que no asume vender arriba del precio de tienda nueva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Comision eBay</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13.25% del precio de venta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Envio</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Estimado por categoria - reemplazalo con tus tarifas reales</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tu API savvy-ebay-prices, endpoint /search-upc (eBay Browse API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Limite de la fuente</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Son listados ACTIVOS (lo que piden), no ventas cerradas. Es el piso competitivo, no el sell-through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -7,20 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Por UPC (consolidado)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Detalle 73 lineas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Alertas datos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Para buscar en eBay" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Resumen por categoria" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Clasificacion Savvy" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Canal MARKETPLACE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Canal PALLET" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Notas y escenarios" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Lotes pallet" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Pallet detalle" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Precios eBay" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="eBay escenarios" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="RESULTADO FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Por UPC (consolidado)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detalle 73 lineas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Alertas datos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Para buscar en eBay" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Resumen por categoria" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Clasificacion Savvy" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Canal MARKETPLACE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Canal PALLET" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Notas y escenarios" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Lotes pallet" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Pallet detalle" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Precios eBay" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Tarifas envio" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77,12 +78,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,144 +450,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Metrica</t>
+          <t>Concepto</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Detalle</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lineas en el manifiesto</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>73</v>
+          <t>RESULTADO FINAL</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UPCs unicos</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>44</v>
+          <t>Costo de la carga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$69,445.70</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Descripciones unicas</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>46</v>
+          <t>Neto estimado</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$19,970.67</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lineas duplicadas (UPC repetido)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Contenedores/pallets</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>31</v>
-      </c>
-    </row>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unidades retail totales</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7053</v>
+          <t>Marketplace (13 UPCs)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>costo $53,225 -&gt; neto $16,122 = ROI 30%</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSRP total</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>172701.04</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Market Price total</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>76353.75</v>
-      </c>
-    </row>
+          <t>Pallet (31 UPCs)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>costo $16,221 -&gt; neto $3,849 = ROI 24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Costo total (sale price)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>69445.7</v>
+          <t>COBERTURA DE DATOS</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Costo como % del MSRP</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>40.2</v>
+          <t>ALTA - UPC exacto en eBay</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21 UPCs</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Costo promedio por unidad retail</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>9.85</v>
+          <t>MEDIA - por nombre, mismo tipo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23 UPCs (precio del tipo de producto, no del modelo exacto)</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Concentracion: top 8 UPCs</t>
+          <t>Sin dato</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>82.0% del costo</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COMO SE CALCULA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>precio conservador x (1 - 13.25% comision eBay) - envio - costo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>50% del retail - costo (sin envio individual, va en tarima)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Precio conservador</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>el menor entre el promedio de eBay y el MSRP. No asume vender arriba de precio de tienda nueva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RIESGO ABIERTO #1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Contenedor E00408C38DCB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SOHO Pitcher w/Elite, UPC 060258364552</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Si la caja trae 2 (como dice)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>140 und a $32.17 c/u -&gt; PIERDE $2,513</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Si la caja trae 8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>482 und a $9.34 c/u -&gt; GANA $2,350</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$4,863 - confirmar con el vendedor antes de pagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LIMITES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Precios</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>listados ACTIVOS de eBay, no ventas cerradas. Es el piso competitivo, no el sell-through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Envio</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ESTIMADO. Ver pestana "Tarifas envio" y reemplazar con tus tarifas reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>API savvy-ebay-prices /search-upc (eBay Browse API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -595,6 +743,1522 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Envio est.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Breakeven eBay</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BE % del MSRP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Neto/und @85%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ROI @85%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>-97</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>283</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>93</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="I4" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>-39</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>88</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="I5" t="n">
+        <v>124</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-10.16</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>-82</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="I7" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>-51</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>144</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-8.84</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>-137</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>52</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>-132</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>-29</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I11" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="I12" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>-126</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="F13" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="I13" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-8.83</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>-137</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="I15" t="n">
+        <v>99</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="I16" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PALLET - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="I17" t="n">
+        <v>99</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PALLET - envio lo mata</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="I18" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PALLET - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="I19" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="I20" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="I21" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="I22" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-7.76</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>-54</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I23" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="I24" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="I25" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>-49</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="I26" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I27" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="I28" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>-76</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="I29" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>-76</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>-138</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="I31" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-10.25</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>-89</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="I32" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>-73</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PALLET - cola larga</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -751,7 +2415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -947,7 +2611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2067,2989 +3731,3109 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="35" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>UPC</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Unidades_retail</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Costo_und</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Envio est.</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Breakeven eBay</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>eBay piso</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>eBay promedio</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>MSRP_und</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>avg/MSRP %</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precio conserv.</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Neto conserv.</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ROI conserv. %</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>listados</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Confianza</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Sospecha multipack</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre en eBay</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>060258359916</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2082</v>
-      </c>
-      <c r="E2" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.48</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="J2" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="K2" t="n">
-        <v>93</v>
-      </c>
-      <c r="L2" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="N2" t="n">
-        <v>43</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Brita Pitcher Replacement Filters #987554 Value Pack Brand New</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>060258355017</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2028</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="K3" t="n">
-        <v>233</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="O3" t="n">
-        <v>14</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>NEW Brita Standard Replacement Carbon Water Filter Model OB03 Pitcher Dispenser</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>060258356182</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>524</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>21.41</v>
-      </c>
-      <c r="H4" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="I4" t="n">
-        <v>65.69</v>
-      </c>
-      <c r="J4" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="K4" t="n">
-        <v>275</v>
-      </c>
-      <c r="L4" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="N4" t="n">
-        <v>23</v>
-      </c>
-      <c r="O4" t="n">
-        <v>20</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Brita Elite Faucet Mount Water Filter System Chrome | Removes 99% of Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>060258509670</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>283</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="F5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>29.72</v>
-      </c>
-      <c r="H5" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I5" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="J5" t="n">
-        <v>29.46</v>
-      </c>
-      <c r="K5" t="n">
-        <v>154</v>
-      </c>
-      <c r="L5" t="n">
-        <v>29.46</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>14</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Brita Water Filter System Original 10 Cup Capacity Pitcher + 1 Filter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>060258362435</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Brita Elite 12/1ct Sidekick Display</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>432</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="H6" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="I6" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="J6" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>143</v>
-      </c>
-      <c r="L6" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N6" t="n">
-        <v>39</v>
-      </c>
-      <c r="O6" t="n">
-        <v>15</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Elite BPA-Free Water Filter Replacement - Reduces 99% Lead, Lasts 120 Gallons</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>060258365153</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>96</v>
-      </c>
-      <c r="E7" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="F7" t="n">
-        <v>14</v>
-      </c>
-      <c r="G7" t="n">
-        <v>32.27</v>
-      </c>
-      <c r="H7" t="n">
-        <v>31.46</v>
-      </c>
-      <c r="I7" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="J7" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>103</v>
-      </c>
-      <c r="L7" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>11</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Brita Large 10 Cup Pacifica White Water Filter Pitcher With Filter</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>060258364606</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>93</v>
-      </c>
-      <c r="E8" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>25.98</v>
-      </c>
-      <c r="H8" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I8" t="n">
-        <v>40.55</v>
-      </c>
-      <c r="J8" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="K8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L8" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="N8" t="n">
-        <v>50</v>
-      </c>
-      <c r="O8" t="n">
-        <v>9</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>NEW Brita Chrome Tap Water Faucet Filtration System with 2 EXTRA Filters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>060258507447</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>144</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G9" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="H9" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="I9" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="K9" t="n">
-        <v>255</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-105</v>
-      </c>
-      <c r="O9" t="n">
-        <v>13</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Metro Water Filter Pitcher with SmartLight Change Indicator, BPA-Free, Replaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>060258364545</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Filtro botella</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>136</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>12.66</v>
-      </c>
-      <c r="H10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="I10" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="J10" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="K10" t="n">
-        <v>162</v>
-      </c>
-      <c r="L10" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="N10" t="n">
-        <v>17</v>
-      </c>
-      <c r="O10" t="n">
-        <v>13</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Brita Water Bottle Replacement Filters, BPA-Free, Replaces 1,800 Plastic Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>060258355031</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>109</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="H11" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="I11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="K11" t="n">
-        <v>175</v>
-      </c>
-      <c r="L11" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="N11" t="n">
-        <v>12</v>
-      </c>
-      <c r="O11" t="n">
-        <v>9</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Brita Tahoe 10 cup Water Filter Brand New Sealed W 9 Filters</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>060258363159</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>40</v>
-      </c>
-      <c r="E12" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="H12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I12" t="n">
-        <v>33.66</v>
-      </c>
-      <c r="J12" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="K12" t="n">
-        <v>101</v>
-      </c>
-      <c r="L12" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>53</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>BRITA Standard Pitcher Replacement Filter - Works in all BRITA Sys Except Stream</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>060258362442</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20.56</v>
-      </c>
-      <c r="H13" t="n">
-        <v>19</v>
-      </c>
-      <c r="I13" t="n">
-        <v>40.75</v>
-      </c>
-      <c r="J13" t="n">
-        <v>28.88</v>
-      </c>
-      <c r="K13" t="n">
-        <v>141</v>
-      </c>
-      <c r="L13" t="n">
-        <v>28.88</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="N13" t="n">
-        <v>61</v>
-      </c>
-      <c r="O13" t="n">
-        <v>18</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Filter Replacements for Water Pitchers and Dispensers 2 Count Blue Plastic</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>060258360899</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>52</v>
-      </c>
-      <c r="E14" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="F14" t="n">
-        <v>14</v>
-      </c>
-      <c r="G14" t="n">
-        <v>23.71</v>
-      </c>
-      <c r="H14" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="I14" t="n">
-        <v>33.06</v>
-      </c>
-      <c r="J14" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="K14" t="n">
-        <v>204</v>
-      </c>
-      <c r="L14" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>-6.53</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-99</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Brita Original Water Filter Pitcher 6-Cup with 1 Filter New</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>060258506884</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>24</v>
-      </c>
-      <c r="E15" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="F15" t="n">
-        <v>14</v>
-      </c>
-      <c r="G15" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="I15" t="n">
-        <v>28.45</v>
-      </c>
-      <c r="J15" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="K15" t="n">
-        <v>85</v>
-      </c>
-      <c r="L15" t="n">
-        <v>28.45</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-20</v>
-      </c>
-      <c r="O15" t="n">
-        <v>6</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Brita Tahoe 10-Cup Water Filter Pitcher + 1 Elite Filter BPA Free</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>060258360936</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E16" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="F16" t="n">
-        <v>14</v>
-      </c>
-      <c r="G16" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="H16" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="K16" t="n">
-        <v>150</v>
-      </c>
-      <c r="L16" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-105</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Brita Soho 5 Cup Pitcher With Filter BPA Free Water Filtration System NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>060258363128</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22.94</v>
-      </c>
-      <c r="I17" t="n">
-        <v>30.52</v>
-      </c>
-      <c r="J17" t="n">
-        <v>23.41</v>
-      </c>
-      <c r="K17" t="n">
-        <v>130</v>
-      </c>
-      <c r="L17" t="n">
-        <v>23.41</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="N17" t="n">
-        <v>53</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Brita Water Filter for Brita Faucet Filtration Systems - Chrome Silver 2 Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>060258363104</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="I18" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="J18" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="K18" t="n">
-        <v>303</v>
-      </c>
-      <c r="L18" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="N18" t="n">
-        <v>11</v>
-      </c>
-      <c r="O18" t="n">
-        <v>8</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>BRITA FR-200 Faucet Mount Replacement Filter, Lead Removal, Chrome, 1 Pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>060258364590</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="F19" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" t="n">
-        <v>26.12</v>
-      </c>
-      <c r="H19" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="I19" t="n">
-        <v>53.27</v>
-      </c>
-      <c r="J19" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>156</v>
-      </c>
-      <c r="L19" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="N19" t="n">
-        <v>51</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Brita Faucet Mount Water Filter System Multi-Use Tap Water Filter for Kitchens</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>060258363098</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H20" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="I20" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>147</v>
-      </c>
-      <c r="L20" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11</v>
-      </c>
-      <c r="O20" t="n">
-        <v>14</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>3 NEW Brita Faucet System Replacement Water Filter Cartridge CHROME FR-200</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>060258364170</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" t="n">
-        <v>18.94</v>
-      </c>
-      <c r="H21" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="I21" t="n">
-        <v>30.63</v>
-      </c>
-      <c r="J21" t="n">
-        <v>26.08</v>
-      </c>
-      <c r="K21" t="n">
-        <v>117</v>
-      </c>
-      <c r="L21" t="n">
-        <v>26.08</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="N21" t="n">
-        <v>59</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Brita standard replacement  Water Filter for Pitchers 6 Count - Sealed</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>060258352146</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="F22" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="H22" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="J22" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="K22" t="n">
-        <v>219</v>
-      </c>
-      <c r="L22" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-40</v>
-      </c>
-      <c r="O22" t="n">
-        <v>20</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Brita On Tap Faucet Filtration System -NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>060258365245</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>18</v>
-      </c>
-      <c r="E23" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="F23" t="n">
-        <v>8</v>
-      </c>
-      <c r="G23" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="H23" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="I23" t="n">
-        <v>27.26</v>
-      </c>
-      <c r="J23" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="K23" t="n">
-        <v>156</v>
-      </c>
-      <c r="L23" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR - tipo no coincide</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>BRITA Premium Leak Proof Filtered Water Bottle • 26 Oz 768ml NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>060258364521</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="H24" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="I24" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>159</v>
-      </c>
-      <c r="L24" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="N24" t="n">
-        <v>16</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR - tipo no coincide</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Premium Stainless Steel Leak Proof Filtered Insulated Water Bottle Brita 20 oz</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>060258362619</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>20</v>
-      </c>
-      <c r="G25" t="n">
-        <v>39.77</v>
-      </c>
-      <c r="H25" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="I25" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="J25" t="n">
-        <v>36.26</v>
-      </c>
-      <c r="K25" t="n">
-        <v>71</v>
-      </c>
-      <c r="L25" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>-12.14</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-84</v>
-      </c>
-      <c r="O25" t="n">
-        <v>6</v>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR - tipo no coincide</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRAND NEW Brita Elite 10-Cup Water Pitcher </t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>060258506846</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>96</v>
-      </c>
-      <c r="E26" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="F26" t="n">
-        <v>14</v>
-      </c>
-      <c r="G26" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="H26" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="K26" t="n">
-        <v>110</v>
-      </c>
-      <c r="L26" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR - pocos listados</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Brita Large 10 Cup White Tahoe Water Filter Pitcher with 1 Standard Filter</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>060258364552</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>140</v>
-      </c>
-      <c r="E27" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="F27" t="n">
-        <v>14</v>
-      </c>
-      <c r="G27" t="n">
-        <v>53.22</v>
-      </c>
-      <c r="H27" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="I27" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="J27" t="n">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="K27" t="n">
-        <v>40</v>
-      </c>
-      <c r="L27" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>-18.94</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-59</v>
-      </c>
-      <c r="O27" t="n">
-        <v>4</v>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Brita Water Filter 6 Cup Denali Water Pitcher Dispenser with Elite Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>060258507263</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>98</v>
-      </c>
-      <c r="E28" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="F28" t="n">
-        <v>14</v>
-      </c>
-      <c r="G28" t="n">
-        <v>33.34</v>
-      </c>
-      <c r="H28" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="I28" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="J28" t="n">
-        <v>37.31</v>
-      </c>
-      <c r="K28" t="n">
-        <v>164</v>
-      </c>
-      <c r="L28" t="n">
-        <v>37.31</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N28" t="n">
-        <v>23</v>
-      </c>
-      <c r="O28" t="n">
-        <v>10</v>
-      </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Brita Wave Elite 10 Cup Smart Water Filter System Pitcher w two filters NEW OB53</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>060258508031</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Brita Hub Filter 6/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>156</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="F29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="H29" t="n">
-        <v>38.48</v>
-      </c>
-      <c r="I29" t="n">
-        <v>41.12</v>
-      </c>
-      <c r="J29" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="K29" t="n">
-        <v>210</v>
-      </c>
-      <c r="L29" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N29" t="n">
-        <v>46</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4</v>
-      </c>
-      <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Brita Hub Replacement Water Filter, BPA-Free, Replaces 900 1 Count, White</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>060258365252</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>48</v>
-      </c>
-      <c r="E30" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="H30" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="I30" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="J30" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="K30" t="n">
-        <v>168</v>
-      </c>
-      <c r="L30" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2</v>
-      </c>
-      <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Brita 36 oz Water Filter Bottle BPA Free with Straw Leakproof Convenient Design</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>060258508956</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>74.76000000000001</v>
-      </c>
-      <c r="F31" t="n">
-        <v>14</v>
-      </c>
-      <c r="G31" t="n">
-        <v>102.32</v>
-      </c>
-      <c r="H31" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="I31" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="J31" t="n">
-        <v>182.34</v>
-      </c>
-      <c r="K31" t="n">
-        <v>9</v>
-      </c>
-      <c r="L31" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>-74.44</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-100</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>060258364668</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>12</v>
-      </c>
-      <c r="E32" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8</v>
-      </c>
-      <c r="G32" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="H32" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="I32" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="J32" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="K32" t="n">
-        <v>263</v>
-      </c>
-      <c r="L32" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>SI - avg inflado</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Brita Hard-Sided Plastic Premium Filtering Water Bottle, 36 Ounces, Orchid</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>060258507027</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="F33" t="n">
-        <v>14</v>
-      </c>
-      <c r="G33" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="H33" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="J33" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="K33" t="n">
-        <v>49</v>
-      </c>
-      <c r="L33" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>-13.42</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-98</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>060258509724</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F34" t="n">
-        <v>20</v>
-      </c>
-      <c r="G34" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="H34" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="I34" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="J34" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="K34" t="n">
-        <v>53</v>
-      </c>
-      <c r="L34" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>-18.48</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-144</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>060258507928</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="F35" t="n">
-        <v>20</v>
-      </c>
-      <c r="G35" t="n">
-        <v>36.37</v>
-      </c>
-      <c r="H35" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="I35" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="J35" t="n">
-        <v>28.88</v>
-      </c>
-      <c r="K35" t="n">
-        <v>57</v>
-      </c>
-      <c r="L35" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>-17.23</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-149</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>DESCARTAR - UPC no existe en eBay</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>060258509878</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>93</v>
-      </c>
-      <c r="E36" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="F36" t="n">
-        <v>14</v>
-      </c>
-      <c r="G36" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="J36" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="L36" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-7</v>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>060258507492</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>88</v>
-      </c>
-      <c r="E37" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="F37" t="n">
-        <v>20</v>
-      </c>
-      <c r="G37" t="n">
-        <v>37.26</v>
-      </c>
-      <c r="J37" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="L37" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>-6.24</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-51</v>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>060258507010</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>96</v>
-      </c>
-      <c r="E38" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="F38" t="n">
-        <v>14</v>
-      </c>
-      <c r="G38" t="n">
-        <v>28.51</v>
-      </c>
-      <c r="J38" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="L38" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-19</v>
-      </c>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>060258506891</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>16</v>
-      </c>
-      <c r="E39" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="F39" t="n">
-        <v>14</v>
-      </c>
-      <c r="G39" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>-27.74</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-202</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>HUGE Lot of 16 Brita Pitcher Replacement Water Filters Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>060258509885</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>28</v>
-      </c>
-      <c r="E40" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="F40" t="n">
-        <v>14</v>
-      </c>
-      <c r="G40" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="J40" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="L40" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>-6.39</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-94</v>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>060258507041</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="F41" t="n">
-        <v>14</v>
-      </c>
-      <c r="G41" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="J41" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="L41" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="N41" t="n">
-        <v>10</v>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>060258507508</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="F42" t="n">
-        <v>20</v>
-      </c>
-      <c r="G42" t="n">
-        <v>50.35</v>
-      </c>
-      <c r="J42" t="n">
-        <v>57.76</v>
-      </c>
-      <c r="L42" t="n">
-        <v>57.76</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="N42" t="n">
-        <v>27</v>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>060258509854</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="F43" t="n">
-        <v>14</v>
-      </c>
-      <c r="G43" t="n">
-        <v>28.21</v>
-      </c>
-      <c r="J43" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="L43" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="N43" t="n">
-        <v>-17</v>
-      </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>060258509410</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F44" t="n">
-        <v>20</v>
-      </c>
-      <c r="G44" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="J44" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="L44" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-45</v>
-      </c>
-      <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>060258509847</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F45" t="n">
-        <v>14</v>
-      </c>
-      <c r="G45" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J45" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="L45" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-105</v>
-      </c>
-      <c r="P45" s="4" t="inlineStr">
-        <is>
-          <t>SIN DATO</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="62" customWidth="1" min="16" max="16"/>
+    <col width="62" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Detalle</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Envio est.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>eBay piso</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>eBay promedio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Precio conserv.</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Neto/und</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Neto total</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Conf. final</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Match UPC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Match nombre</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Universo</t>
+          <t>060258359916</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Los 21 UPCs de confianza ALTA = $56,675 = 81.6% del costo de la carga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="K2" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>14220.06</v>
+      </c>
+      <c r="N2" t="n">
+        <v>43</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Brita Pitcher Replacement Filters #987554 Value Pack Brand New</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1379.04</v>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NEW Brita Standard Replacement Carbon Water Filter Model OB03 Pitcher Dispenser</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Si vendes al PISO (igualando al mas barato)</t>
+          <t>060258362435</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>neto -$9,404  = ROI -17%  | solo 8 de 21 SKUs rentables</t>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>432</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1166.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Elite BPA-Free Water Filter Replacement - Reduces 99% Lead, Lasts 120 Gallons</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Si vendes al PROMEDIO de eBay</t>
+          <t>060258356182</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>neto +$62,249 = ROI 110% | 20 de 21 rentables  (OJO: promedio inflado por multipacks)</t>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>524</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="I5" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="K5" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1142.32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brita Elite Faucet Mount Water Filter System Chrome | Removes 99% of Lead</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Si vendes CONSERVADOR (tope = MSRP)</t>
+          <t>060258509670</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>neto +$12,981 = ROI 23%  | 14 de 21 rentables</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>283</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="I6" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="K6" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>834.85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brita Water Filter System Original 10 Cup Capacity Pitcher + 1 Filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>93</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="K7" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>635.1900000000001</v>
+      </c>
+      <c r="N7" t="n">
+        <v>50</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NEW Brita Chrome Tap Water Faucet Filtration System with 2 EXTRA Filters</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Por que el promedio esta inflado</t>
+          <t>060258508031</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>En 10 SKUs el promedio de eBay supera 150% del MSRP. Eso pasa cuando listados de multipack se cuelan en el promedio de un producto de 1 unidad. No asumas ese precio.</t>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>156</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="K8" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>566.28</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brita Hub Replacement Water Filter, BPA-Free, Replaces 900 1 Count, White</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Brita Elite Faucet Mount Water Filter System Chrome With 2 Filters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cual usar</t>
+          <t>060258362442</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>El CONSERVADOR. Es el unico que no asume vender arriba del precio de tienda nueva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="K9" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>61</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Filter Replacements for Water Pitchers and Dispensers 2 Count Blue Plastic</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I10" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="K10" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>282.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>53</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>BRITA Standard Pitcher Replacement Filter - Works in all BRITA Sys Except Stream</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Comision eBay</t>
+          <t>060258509878</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13.25% del precio de venta</t>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="I11" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>240.87</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Brita Water Filter Pitcher  6 Cup with 1 Standard Filter, BPA Free - Blue</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Envio</t>
+          <t>060258507492</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Estimado por categoria - reemplazalo con tus tarifas reales</t>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="I12" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="K12" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>238.48</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Brita Extra Large 27-Cup UltraMax Filtered Water Dispenser with Filter - Gray:</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fuente</t>
+          <t>060258506846</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tu API savvy-ebay-prices, endpoint /search-upc (eBay Browse API)</t>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>96</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="I13" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>22</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brita Large 10 Cup White Tahoe Water Filter Pitcher with 1 Standard Filter</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10-Cup Water Filter Pitcher</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Limite de la fuente</t>
+          <t>060258507010</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Son listados ACTIVOS (lo que piden), no ventas cerradas. Es el piso competitivo, no el sell-through.</t>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>96</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="I14" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="K14" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>226.56</v>
+      </c>
+      <c r="N14" t="n">
+        <v>22</v>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher Bright White 6 Cups Smart Light Indicator 62047 /AR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>060258507447</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>144</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14</v>
+      </c>
+      <c r="H15" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="I15" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>204.48</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Metro Water Filter Pitcher with SmartLight Change Indicator, BPA-Free, Replaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>96</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="I16" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="K16" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brita Large 10 Cup Pacifica White Water Filter Pitcher With Filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>136</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="I17" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="J17" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>123.76</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brita Water Bottle Replacement Filters, BPA-Free, Replaces 1,800 Plastic Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="I18" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="K18" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="N18" t="n">
+        <v>25</v>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brita 36 oz Water Filter Bottle BPA Free with Straw Leakproof Convenient Design</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Brita 32oz Stainless Steel Filter Water Bottle Leakproof Straw BPA Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>109</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="I19" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="K19" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>79.56999999999999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>12</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10 cup Water Filter Brand New Sealed W 9 Filters</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>52</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="I20" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="N20" t="n">
+        <v>23</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brita Original Water Filter Pitcher 6-Cup with 1 Filter New</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>29</v>
+      </c>
+      <c r="I21" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K21" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>22</v>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>HUGE Lot of 16 Brita Pitcher Replacement Water Filters Standard</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10-Cup Water Filter Pitcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>98</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14</v>
+      </c>
+      <c r="H22" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="I22" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="J22" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="K22" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brita Wave Elite 10 Cup Smart Water Filter System Pitcher w two filters NEW OB53</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Brita  10 Cup Water Filter Pitcher White Pacifica with 1 Elite Filter BPA Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>28</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="I23" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="J23" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="K23" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>22</v>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Brita Water Filter Pitcher  6 Cup with 1 Standard Filter, BPA Free - Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14</v>
+      </c>
+      <c r="H24" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="N24" t="n">
+        <v>22</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brita Soho 5 Cup Pitcher With Filter BPA Free Water Filtration System NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="J25" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="K25" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="L25" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="N25" t="n">
+        <v>22</v>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Brita Water Filter Pitcher  6 Cup with 1 Standard Filter, BPA Free - Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="I26" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="J26" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="K26" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="N26" t="n">
+        <v>25</v>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>BRITA Premium Leak Proof Filtered Water Bottle • 26 Oz 768ml NEW</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Brita Hard-Sided Plastic Premium Filtering Water Bottle, Sea Glass - 36 oz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="I27" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="J27" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="K27" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brita Water Filter for Brita Faucet Filtration Systems - Chrome Silver 2 Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="I28" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="J28" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="K28" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="N28" t="n">
+        <v>25</v>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brita Hard-Sided Plastic Premium Filtering Water Bottle, 36 Ounces, Orchid</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Brita Hard-Sided Plastic Premium Filtering Water Bottle, 36 Ounces, Orchid</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="I29" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="J29" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K29" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="N29" t="n">
+        <v>25</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>BRITA FR-200 Faucet Mount Replacement Filter, Lead Removal, Chrome, 1 Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="I30" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="K30" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="N30" t="n">
+        <v>25</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brita Faucet Mount Water Filter System Multi-Use Tap Water Filter for Kitchens</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="I31" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="J31" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="N31" t="n">
+        <v>22</v>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Premium Stainless Steel Leak Proof Filtered Insulated Water Bottle Brita 20 oz</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>BRITA Stainless Steel Premium Water Bottle with Filter 32 oz Rose BPA-Free - NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="J32" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K32" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="N32" t="n">
+        <v>25</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>3 NEW Brita Faucet System Replacement Water Filter Cartridge CHROME FR-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="I33" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="J33" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="K33" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="N33" t="n">
+        <v>25</v>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRAND NEW Brita Elite 10-Cup Water Pitcher </t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Brita Extra Large 27-Cup UltraMax Filtered Water Dispenser with Filter - Gray:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I34" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="J34" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K34" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="N34" t="n">
+        <v>22</v>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Brita Water Filter Pitcher  6 Cup with 1 Standard Filter, BPA Free - Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="K35" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="N35" t="n">
+        <v>25</v>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10-Cup Water Filter Pitcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="I36" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="J36" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="K36" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="N36" t="n">
+        <v>25</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Brita standard replacement  Water Filter for Pitchers 6 Count - Sealed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="I37" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="J37" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="K37" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>22</v>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Brita UltraMax 27 Cup Water Filter Dispenser Black Large Fridge Pitcher BPA Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>14</v>
+      </c>
+      <c r="H38" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="I38" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="J38" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="K38" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N38" t="n">
+        <v>25</v>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10-Cup Water Filter Pitcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G39" t="n">
+        <v>14</v>
+      </c>
+      <c r="H39" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I39" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="J39" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K39" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N39" t="n">
+        <v>22</v>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Brita Water Filter Pitcher  6 Cup with 1 Standard Filter, BPA Free - Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G40" t="n">
+        <v>20</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="I40" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="J40" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="K40" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N40" t="n">
+        <v>25</v>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Brita Extra Large 27-Cup UltraMax Filtered Water Dispenser with Filter - Gray:</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="J41" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="K41" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N41" t="n">
+        <v>25</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brita On Tap Faucet Filtration System -NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G42" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="I42" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="J42" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="K42" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N42" t="n">
+        <v>22</v>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Brita Extra Large 27-Cup UltraMax Filtered Water Dispenser with Filter - Gray:</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="I43" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="J43" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="K43" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N43" t="n">
+        <v>22</v>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>FIRST LP + 13 BONUS TRACKS NEW CD</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Brita Extra Large 27-Cup UltraMax Filtered Water Dispenser with Filter - Gray:</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G44" t="n">
+        <v>14</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="I44" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="J44" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K44" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>-65.52</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brita Tahoe 10-Cup Water Filter Pitcher + 1 Elite Filter BPA Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>140</v>
+      </c>
+      <c r="F45" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="G45" t="n">
+        <v>14</v>
+      </c>
+      <c r="H45" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="I45" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="J45" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="K45" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-17.95</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>-2513</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-56</v>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Brita Water Filter 6 Cup Denali Water Pitcher Dispenser with Elite Water</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Brita Large 10 Cup Water Filter Pitcher W/ Brita Elite Filter White NEW SEALED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mi estimado $</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>TU TARIFA REAL $ &lt;- LLENAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher 1ct</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>~5 oz, sobre acolchado</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Filtro pitcher 2ct</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Filtro pitcher 3ct</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Filtro pitcher 8ct</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Filtro pitcher 10ct</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>~2 lb, caja 10x6x6</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Filtro Hub</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Filtro botella 6ct</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sistema grifo (On Tap)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>~1.5 lb, caja 8x7x4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Botella filtrante</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>~1 lb</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pitcher 6-10 cup</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>~2.5 lb pero caja 11x11x11 (peso dimensional)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dispenser 18-27 cup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>caja grande</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5058,6 +6842,158 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metrica</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lineas en el manifiesto</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UPCs unicos</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Descripciones unicas</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lineas duplicadas (UPC repetido)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Contenedores/pallets</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Unidades retail totales</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7053</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MSRP total</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>172701.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Market Price total</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>76353.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Costo total (sale price)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>69445.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Costo como % del MSRP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Costo promedio por unidad retail</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Concentracion: top 8 UPCs</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>82.0% del costo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6849,7 +8785,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10774,7 +12710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10956,7 +12892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11790,7 +13726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12012,7 +13948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13938,7 +15874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14624,1520 +16560,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>UPC</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Unidades_retail</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MSRP_und</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Costo_und</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Envio est.</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Breakeven eBay</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BE % del MSRP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Neto/und @85%</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ROI @85%</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Canal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>060258355017</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>-97</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>060258509670</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>283</v>
-      </c>
-      <c r="E3" t="n">
-        <v>29.46</v>
-      </c>
-      <c r="F3" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H3" t="n">
-        <v>29.72</v>
-      </c>
-      <c r="I3" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-34</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>060258509878</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>93</v>
-      </c>
-      <c r="E4" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H4" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="I4" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-4.61</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-39</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>060258507492</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>88</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" t="n">
-        <v>37.26</v>
-      </c>
-      <c r="I5" t="n">
-        <v>124</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-10.16</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>-82</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>060258506846</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>96</v>
-      </c>
-      <c r="E6" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14</v>
-      </c>
-      <c r="H6" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-5.24</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>060258507010</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>96</v>
-      </c>
-      <c r="E7" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14</v>
-      </c>
-      <c r="H7" t="n">
-        <v>28.51</v>
-      </c>
-      <c r="I7" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>-51</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>060258507447</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>144</v>
-      </c>
-      <c r="E8" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="G8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="I8" t="n">
-        <v>149.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-8.84</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>-137</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>060258360899</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>52</v>
-      </c>
-      <c r="E9" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="G9" t="n">
-        <v>14</v>
-      </c>
-      <c r="H9" t="n">
-        <v>23.71</v>
-      </c>
-      <c r="I9" t="n">
-        <v>146.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-8.640000000000001</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>-132</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>060258365252</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>48</v>
-      </c>
-      <c r="E10" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="F10" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="I10" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>-29</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>060258506891</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E11" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="F11" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="G11" t="n">
-        <v>14</v>
-      </c>
-      <c r="H11" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="I11" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>060258509885</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="G12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H12" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="I12" t="n">
-        <v>144.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-8.550000000000001</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>-126</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>060258508956</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>182.34</v>
-      </c>
-      <c r="F13" t="n">
-        <v>74.76000000000001</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14</v>
-      </c>
-      <c r="H13" t="n">
-        <v>102.32</v>
-      </c>
-      <c r="I13" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>45.69</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>060258360936</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>23</v>
-      </c>
-      <c r="E14" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14</v>
-      </c>
-      <c r="H14" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-8.83</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>-137</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>060258365245</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>18</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="G15" t="n">
-        <v>8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="I15" t="n">
-        <v>99</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>060258363128</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11</v>
-      </c>
-      <c r="E16" t="n">
-        <v>23.41</v>
-      </c>
-      <c r="F16" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="I16" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>PALLET - poco volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>060258364668</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="I17" t="n">
-        <v>99</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>PALLET - envio lo mata</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>060258363104</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12</v>
-      </c>
-      <c r="E18" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="I18" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>PALLET - poco volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>060258364590</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="F19" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="G19" t="n">
-        <v>9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>26.12</v>
-      </c>
-      <c r="I19" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>060258364521</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="I20" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>060258363098</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="I21" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>060258362619</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>36.26</v>
-      </c>
-      <c r="F22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>20</v>
-      </c>
-      <c r="H22" t="n">
-        <v>39.77</v>
-      </c>
-      <c r="I22" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-7.76</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>-54</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>060258507041</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="F23" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="G23" t="n">
-        <v>14</v>
-      </c>
-      <c r="H23" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="I23" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>060258507508</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>57.76</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="G24" t="n">
-        <v>20</v>
-      </c>
-      <c r="H24" t="n">
-        <v>50.35</v>
-      </c>
-      <c r="I24" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>060258509854</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="F25" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="G25" t="n">
-        <v>14</v>
-      </c>
-      <c r="H25" t="n">
-        <v>28.21</v>
-      </c>
-      <c r="I25" t="n">
-        <v>107.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>-49</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>060258364170</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>26.08</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>18.94</v>
-      </c>
-      <c r="I26" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>060258507027</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="F27" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="G27" t="n">
-        <v>14</v>
-      </c>
-      <c r="H27" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="I27" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>060258509724</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="F28" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G28" t="n">
-        <v>20</v>
-      </c>
-      <c r="H28" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="I28" t="n">
-        <v>121.1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-9.77</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>-76</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>060258509410</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="F29" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>20</v>
-      </c>
-      <c r="H29" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="I29" t="n">
-        <v>121.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-9.77</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>-76</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>060258509847</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G30" t="n">
-        <v>14</v>
-      </c>
-      <c r="H30" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>148.6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-8.68</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>-138</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>060258507928</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>28.88</v>
-      </c>
-      <c r="F31" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="G31" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" t="n">
-        <v>36.37</v>
-      </c>
-      <c r="I31" t="n">
-        <v>125.9</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-10.25</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>-89</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>060258352146</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="F32" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="G32" t="n">
-        <v>9</v>
-      </c>
-      <c r="H32" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="I32" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>-73</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>PALLET - cola larga</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -78,13 +78,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -709,7 +710,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ESTIMADO. Ver pestana "Tarifas envio" y reemplazar con tus tarifas reales.</t>
+          <t>CONFIRMADAS por Octavio (29-sep-2026). Ver pestana "Tarifas envio".</t>
         </is>
       </c>
     </row>
@@ -6655,13 +6656,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6675,14 +6675,9 @@
           <t>Nota</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mi estimado $</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>TU TARIFA REAL $ &lt;- LLENAR</t>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Tarifa usada $ (CONFIRMADA por Octavio 29-sep-2026)</t>
         </is>
       </c>
     </row>

--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Pallet detalle" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Precios eBay" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Tarifas envio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Sensibilidad envio" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -710,7 +711,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CONFIRMADAS por Octavio (29-sep-2026). Ver pestana "Tarifas envio".</t>
+          <t>APROXIMADO. Validado de vista por Octavio (29-sep-2026). Cada $1 de diferencia mueve $3,970 - ver pestana "Sensibilidad envio".</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6662,7 @@
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="61" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6675,9 +6676,9 @@
           <t>Nota</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Tarifa usada $ (CONFIRMADA por Octavio 29-sep-2026)</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tarifa usada $ (APROXIMADA - validada de vista por Octavio)</t>
         </is>
       </c>
     </row>
@@ -6829,6 +6830,169 @@
       </c>
       <c r="C13" t="n">
         <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cada $1 de diferencia en el envio = $3,970 en el resultado final (3,970 unidades van por marketplace).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Si el envio real resulta</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Neto total</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>-$3 por unidad</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$31,888</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>-$2 por unidad</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$27,918</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>-$1 por unidad</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$23,948</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>COMO SE ESTIMO</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>$19,978</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>+$1 por unidad</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$16,008</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>+$2 por unidad</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>$12,038</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>+$3 por unidad</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>$8,068</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -7,22 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RESULTADO FINAL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Por UPC (consolidado)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Detalle 73 lineas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Alertas datos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Para buscar en eBay" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Resumen por categoria" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Clasificacion Savvy" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Canal MARKETPLACE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Canal PALLET" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Notas y escenarios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Lotes pallet" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Pallet detalle" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Precios eBay" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Tarifas envio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Sensibilidad envio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SAVVY vs DWI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Savvy vs DWI sensib" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Savvy vs DWI detalle" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RESULTADO FINAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resumen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Por UPC (consolidado)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Detalle 73 lineas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Alertas datos" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Para buscar en eBay" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Resumen por categoria" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Clasificacion Savvy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Canal MARKETPLACE" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Canal PALLET" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Notas y escenarios" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Lotes pallet" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Pallet detalle" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Precios eBay" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Tarifas envio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Sensibilidad envio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +47,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +69,16 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -79,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +100,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,288 +469,408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Detalle</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SKUs</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>% SKUs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>% unidades</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>% costo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RESULTADO FINAL</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>SAVVY (retail por unidad)</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>2860</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>$39,339</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>$17,253</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Costo de la carga</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>$69,445.70</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>DWI (lote mas barato)</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>4193</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>$30,107</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>$7,148</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>24%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Neto estimado</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$19,970.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>29%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7053</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>$69,446</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>$24,402</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marketplace (13 UPCs)</t>
+          <t>Concepto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>costo $53,225 -&gt; neto $16,122 = ROI 30%</t>
+          <t>Detalle</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pallet (31 UPCs)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>costo $16,221 -&gt; neto $3,849 = ROI 24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>LA REGLA</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="1" t="n"/>
+      <c r="I8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Savvy $/und</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>precio eBay conservador x (1 - 13.25% comision) - envio - costo</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COBERTURA DE DATOS</t>
+          <t>DWI $/und</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>50% del retail - costo (sin envio individual, va en tarima)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALTA - UPC exacto en eBay</t>
+          <t>Cada SKU va</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21 UPCs</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MEDIA - por nombre, mismo tipo</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>23 UPCs (precio del tipo de producto, no del modelo exacto)</t>
-        </is>
-      </c>
-    </row>
+          <t>al canal que paga mas. La columna "Ventaja/und" dice cuanto gana Savvy sobre DWI (negativo = gana DWI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sin dato</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>LA RESPUESTA CORTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Para Savvy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9 SKUs de 44 (20%), pero son 57% del dinero y 71% de la utilidad</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMO SE CALCULA</t>
+          <t>Para DWI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>35 SKUs de 44 (80%), 43% del dinero y 29% de la utilidad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Por que</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>precio conservador x (1 - 13.25% comision eBay) - envio - costo</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pallet</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>50% del retail - costo (sin envio individual, va en tarima)</t>
-        </is>
-      </c>
-    </row>
+          <t>Savvy solo gana donde el producto es chico y ligero: filtros y sistemas de grifo. Todo lo voluminoso (pitchers, dispensers, botellas) lo gana DWI porque en lote no paga envio individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Precio conservador</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>el menor entre el promedio de eBay y el MSRP. No asume vender arriba de precio de tienda nueva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RIESGO ABIERTO #1</t>
-        </is>
-      </c>
-    </row>
+          <t>EL SKU QUE MANDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258359916 Filtros 10-pack</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2,082 und -&gt; $14,220 de utilidad = 58% del total de la carga. Va a SAVVY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Contenedor E00408C38DCB</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SOHO Pitcher w/Elite, UPC 060258364552</t>
+          <t>CASOS AL FILO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Si la caja trae 2 (como dice)</t>
+          <t>060258356182 On Tap Chrome</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>140 und a $32.17 c/u -&gt; PIERDE $2,513</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Si la caja trae 8</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>482 und a $9.34 c/u -&gt; GANA $2,350</t>
-        </is>
-      </c>
-    </row>
+          <t>524 und. Savvy $2.18 vs DWI $2.39 - diferencia de 21 centavos. Cualquiera de los dos sirve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Swing</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>$4,863 - confirmar con el vendedor antes de pagar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
+          <t>SUPUESTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DWI al 50% del retail</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Es el default de tu Savvy Scanner. Si DWI vende a otro precio el reparto cambia - ver pestana "Savvy vs DWI sensib".</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LIMITES</t>
+          <t>Comision eBay</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13.25%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Precios</t>
+          <t>Envio</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>listados ACTIVOS de eBay, no ventas cerradas. Es el piso competitivo, no el sell-through.</t>
+          <t>Aproximado, validado por Octavio</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Envio</t>
+          <t>Precios eBay</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>APROXIMADO. Validado de vista por Octavio (29-sep-2026). Cada $1 de diferencia mueve $3,970 - ver pestana "Sensibilidad envio".</t>
+          <t>Listados activos, no ventas cerradas</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fuente</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
-        <is>
-          <t>API savvy-ebay-prices /search-upc (eBay Browse API)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
@@ -745,6 +882,2842 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UPCs</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>% costo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44185.15144</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1198</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16198.0989</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>623</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6339.34384</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1174.415</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>136</v>
+      </c>
+      <c r="D6" t="n">
+        <v>745.8240000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>84</v>
+      </c>
+      <c r="D7" t="n">
+        <v>597.839959</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" t="n">
+        <v>205.028</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SI - poco volumen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Consumible</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Costo_total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>% del costo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32707.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5589.168000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258362435</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>432</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2967.552</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258508031</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1219.53144</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>136</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>745.8240000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>109</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>674.564</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="H8" t="n">
+        <v>532.64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>473.632</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SI - nucleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>103.004</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SI - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>68.01600000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SI - poco volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H12" t="n">
+        <v>34.008</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20.864</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>524</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5013.632000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F15" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4503.755200000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>283</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3334.872</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>98</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1462.552</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>96</v>
+      </c>
+      <c r="F18" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1342.5696</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>93</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1259.592</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>93</v>
+      </c>
+      <c r="F20" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1093.1871</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>88</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1084.5648</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NO - cola larga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>96</v>
+      </c>
+      <c r="F22" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1053.6672</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>96</v>
+      </c>
+      <c r="F23" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1030.4448</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>144</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H24" t="n">
+        <v>929.88</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>52</v>
+      </c>
+      <c r="F25" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="H25" t="n">
+        <v>341.7968</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>48</v>
+      </c>
+      <c r="F26" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H26" t="n">
+        <v>338.496</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="H27" t="n">
+        <v>321.792</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H28" t="n">
+        <v>219.8912</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>28</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="H29" t="n">
+        <v>190.7976</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="G30" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>149.5188</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>23</v>
+      </c>
+      <c r="F31" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H31" t="n">
+        <v>148.601</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MIXTO - depende del volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>18</v>
+      </c>
+      <c r="F32" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H32" t="n">
+        <v>125.496</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H33" t="n">
+        <v>83.664</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MIXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="H34" t="n">
+        <v>54.65584</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>50.183959</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>29.008</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H37" t="n">
+        <v>27.4864</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="G38" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>23.6816</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="H39" t="n">
+        <v>20.944</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="G40" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13.7432</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="G41" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12.8043</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="G42" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.8043</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="G44" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H44" t="n">
+        <v>11.552</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="H45" t="n">
+        <v>11.464</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NO - cola larga (&lt;=10 und)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades_retail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP_und</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo_und</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Envio est.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Breakeven eBay</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BE % del MSRP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Neto/und @85%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ROI @85%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>524</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="I3" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>140</v>
+      </c>
+      <c r="E4" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258362435</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>432</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>98</v>
+      </c>
+      <c r="E6" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="I6" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E7" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="I7" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>93</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="I8" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>060258508031</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>156</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>136</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I10" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>109</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="I11" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="F12" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="I13" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MARKETPLACE - marginal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2260,7 +5233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2417,7 +5390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2613,7 +5586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3733,7 +6706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6651,7 +9624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6837,7 +9810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6858,7 +9831,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -7001,6 +9973,3324 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Si DWI vende el lote a</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SAVVY se queda con</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DWI se queda con</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Neto total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>40% del retail</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24 SKUs / 3,945 und / 71% del costo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20 SKUs / 3,108 und / 29%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>$18,602</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>45% del retail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13 SKUs / 3,622 und / 67%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>31 SKUs / 3,431 und / 33%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>$21,258</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>50% del retail (lo que usa tu Scanner)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>9 SKUs / 2,860 und / 57%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>35 SKUs / 4,193 und / 43%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>$24,402</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>55% del retail</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9 SKUs / 2,860 und / 57%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>35 SKUs / 4,193 und / 43%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>$28,139</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>60% del retail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6 SKUs / 190 und / 4%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>38 SKUs / 6,863 und / 96%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>$34,257</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="51" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mejor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo/und</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Envio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Precio conserv.</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Savvy $/und</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DWI $/und</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ventaja/und</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Neto/und</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Neto total</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>MSRP/und</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Confianza</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confianza</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1379.04</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>524</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1252.36</v>
+      </c>
+      <c r="N3" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>140</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-17.95</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-25.06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="M4" t="n">
+        <v>995.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>283</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M5" t="n">
+        <v>834.85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>98</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="M6" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>96</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>293.76</v>
+      </c>
+      <c r="N7" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>93</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M8" t="n">
+        <v>240.87</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>88</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M9" t="n">
+        <v>238.48</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>96</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>REVISAR - pocos listados</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>96</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M11" t="n">
+        <v>226.56</v>
+      </c>
+      <c r="N11" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>144</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>204.48</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>136</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M13" t="n">
+        <v>187.68</v>
+      </c>
+      <c r="N13" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>109</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M14" t="n">
+        <v>167.86</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="N15" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M16" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>52</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-6.53</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M17" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M18" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="N18" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>28</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>42</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-6.77</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M20" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="N20" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-59.62</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-76.03</v>
+      </c>
+      <c r="L21" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="M21" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="N21" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M22" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="N22" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>REVISAR - tipo no coincide</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M24" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="N24" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>REVISAR - tipo no coincide</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="N26" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M27" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="N27" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>REVISAR - tipo no coincide</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14</v>
+      </c>
+      <c r="H28" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="N28" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="N29" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G32" t="n">
+        <v>14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N33" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N34" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-8.52</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N35" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-8.52</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N36" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>SIN DATO</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F37" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G37" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M37" t="n">
+        <v>14220.06</v>
+      </c>
+      <c r="N37" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>060258362435</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>432</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1166.4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>93</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M39" t="n">
+        <v>635.1900000000001</v>
+      </c>
+      <c r="N39" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>060258508031</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>156</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M40" t="n">
+        <v>566.28</v>
+      </c>
+      <c r="N40" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>DESCARTAR - UPC no existe en eBay</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>40</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="M41" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="N41" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>40</v>
+      </c>
+      <c r="F42" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="M42" t="n">
+        <v>282.4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>11</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M43" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="N43" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L44" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M44" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="N44" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M45" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="N45" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RESULTADO FINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Costo de la carga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$69,445.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Neto estimado</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$19,970.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Marketplace (13 UPCs)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>costo $53,225 -&gt; neto $16,122 = ROI 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pallet (31 UPCs)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>costo $16,221 -&gt; neto $3,849 = ROI 24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>COBERTURA DE DATOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto en eBay</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21 UPCs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre, mismo tipo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23 UPCs (precio del tipo de producto, no del modelo exacto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COMO SE CALCULA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>precio conservador x (1 - 13.25% comision eBay) - envio - costo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>50% del retail - costo (sin envio individual, va en tarima)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Precio conservador</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>el menor entre el promedio de eBay y el MSRP. No asume vender arriba de precio de tienda nueva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RIESGO ABIERTO #1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Contenedor E00408C38DCB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SOHO Pitcher w/Elite, UPC 060258364552</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Si la caja trae 2 (como dice)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>140 und a $32.17 c/u -&gt; PIERDE $2,513</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Si la caja trae 8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>482 und a $9.34 c/u -&gt; GANA $2,350</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$4,863 - confirmar con el vendedor antes de pagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LIMITES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Precios</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>listados ACTIVOS de eBay, no ventas cerradas. Es el piso competitivo, no el sell-through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Envio</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>APROXIMADO. Validado de vista por Octavio (29-sep-2026). Cada $1 de diferencia mueve $3,970 - ver pestana "Sensibilidad envio".</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>API savvy-ebay-prices /search-upc (eBay Browse API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7152,7 +13442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8944,7 +15234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12869,7 +19159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13051,7 +19341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13883,2840 +20173,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>UPCs</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Unidades</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Costo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>% costo</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Veredicto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4889</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44185.15144</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1198</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16198.0989</v>
-      </c>
-      <c r="E3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>623</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6339.34384</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>94</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1174.415</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NO - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Filtro botella</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>136</v>
-      </c>
-      <c r="D6" t="n">
-        <v>745.8240000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>84</v>
-      </c>
-      <c r="D7" t="n">
-        <v>597.839959</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MIXTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>29</v>
-      </c>
-      <c r="D8" t="n">
-        <v>205.028</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SI - poco volumen</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>UPC</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Consumible</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Unidades_retail</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>MSRP_und</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Costo_und</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Costo_total</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>% del costo</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Veredicto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>060258359916</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2082</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="G2" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32707.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>060258355017</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5589.168000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>060258362435</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brita Elite 12/1ct Sidekick Display</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>432</v>
-      </c>
-      <c r="F4" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2967.552</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>060258508031</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brita Hub Filter 6/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>156</v>
-      </c>
-      <c r="F5" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1219.53144</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>060258364545</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Filtro botella</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>136</v>
-      </c>
-      <c r="F6" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="H6" t="n">
-        <v>745.8240000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>060258355031</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>109</v>
-      </c>
-      <c r="F7" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="H7" t="n">
-        <v>674.564</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>060258363159</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>40</v>
-      </c>
-      <c r="F8" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="H8" t="n">
-        <v>532.64</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>060258362442</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>40</v>
-      </c>
-      <c r="F9" t="n">
-        <v>28.88</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="H9" t="n">
-        <v>473.632</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>SI - nucleo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>060258363128</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" t="n">
-        <v>23.41</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>103.004</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>SI - poco volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>060258363104</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>12</v>
-      </c>
-      <c r="F11" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="H11" t="n">
-        <v>68.01600000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>SI - poco volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>060258363098</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Filtro grifo</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="H12" t="n">
-        <v>34.008</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>060258364170</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>26.08</v>
-      </c>
-      <c r="G13" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="H13" t="n">
-        <v>20.864</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>060258356182</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>524</v>
-      </c>
-      <c r="F14" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="G14" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5013.632000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>060258364552</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>140</v>
-      </c>
-      <c r="F15" t="n">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="G15" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4503.755200000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>060258509670</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>283</v>
-      </c>
-      <c r="F16" t="n">
-        <v>29.46</v>
-      </c>
-      <c r="G16" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3334.872</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>060258507263</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>98</v>
-      </c>
-      <c r="F17" t="n">
-        <v>37.31</v>
-      </c>
-      <c r="G17" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1462.552</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>060258365153</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>96</v>
-      </c>
-      <c r="F18" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="G18" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1342.5696</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>060258364606</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>93</v>
-      </c>
-      <c r="F19" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="G19" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1259.592</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>060258509878</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>93</v>
-      </c>
-      <c r="F20" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="G20" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1093.1871</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>060258507492</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>88</v>
-      </c>
-      <c r="F21" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="G21" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1084.5648</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NO - cola larga</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>060258506846</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>96</v>
-      </c>
-      <c r="F22" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="G22" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1053.6672</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>060258507010</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>96</v>
-      </c>
-      <c r="F23" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="G23" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1030.4448</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>060258507447</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>144</v>
-      </c>
-      <c r="F24" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="H24" t="n">
-        <v>929.88</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>060258360899</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>52</v>
-      </c>
-      <c r="F25" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="H25" t="n">
-        <v>341.7968</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>060258365252</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>48</v>
-      </c>
-      <c r="F26" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="H26" t="n">
-        <v>338.496</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>MIXTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>060258506884</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>24</v>
-      </c>
-      <c r="F27" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="G27" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="H27" t="n">
-        <v>321.792</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>060258506891</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>16</v>
-      </c>
-      <c r="F28" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="G28" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="H28" t="n">
-        <v>219.8912</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>060258509885</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>28</v>
-      </c>
-      <c r="F29" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="H29" t="n">
-        <v>190.7976</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>060258508956</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>182.34</v>
-      </c>
-      <c r="G30" t="n">
-        <v>74.76000000000001</v>
-      </c>
-      <c r="H30" t="n">
-        <v>149.5188</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>060258360936</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>23</v>
-      </c>
-      <c r="F31" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="H31" t="n">
-        <v>148.601</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>MIXTO - depende del volumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>060258365245</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>18</v>
-      </c>
-      <c r="F32" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="H32" t="n">
-        <v>125.496</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>MIXTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>060258364668</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>12</v>
-      </c>
-      <c r="F33" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="H33" t="n">
-        <v>83.664</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>MIXTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>060258364590</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="G34" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="H34" t="n">
-        <v>54.65584</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>060258364521</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Botella</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6</v>
-      </c>
-      <c r="F35" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="H35" t="n">
-        <v>50.183959</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>060258362619</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>36.26</v>
-      </c>
-      <c r="G36" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>29.008</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>060258507041</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="G37" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="H37" t="n">
-        <v>27.4864</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>060258507508</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>57.76</v>
-      </c>
-      <c r="G38" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="H38" t="n">
-        <v>23.6816</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>060258509854</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="G39" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="H39" t="n">
-        <v>20.944</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>060258507027</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="G40" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="H40" t="n">
-        <v>13.7432</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>060258509724</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="G41" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H41" t="n">
-        <v>12.8043</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>060258509410</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="G42" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H42" t="n">
-        <v>12.8043</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>060258509847</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H43" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>060258507928</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Dispenser</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>28.88</v>
-      </c>
-      <c r="G44" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="H44" t="n">
-        <v>11.552</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>060258352146</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="H45" t="n">
-        <v>11.464</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>NO - cola larga (&lt;=10 und)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>UPC</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Unidades_retail</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MSRP_und</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Costo_und</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Envio est.</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Breakeven eBay</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BE % del MSRP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Neto/und @85%</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ROI @85%</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Canal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>060258359916</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2082</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="F2" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.48</v>
-      </c>
-      <c r="I2" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - fuerte</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>060258356182</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>524</v>
-      </c>
-      <c r="E3" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="F3" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>21.41</v>
-      </c>
-      <c r="I3" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>060258364552</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>140</v>
-      </c>
-      <c r="E4" t="n">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="F4" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H4" t="n">
-        <v>53.22</v>
-      </c>
-      <c r="I4" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - fuerte</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>060258362435</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brita Elite 12/1ct Sidekick Display</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>432</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="I5" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>060258507263</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>98</v>
-      </c>
-      <c r="E6" t="n">
-        <v>37.31</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33.34</v>
-      </c>
-      <c r="I6" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>060258365153</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>96</v>
-      </c>
-      <c r="E7" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="F7" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14</v>
-      </c>
-      <c r="H7" t="n">
-        <v>32.27</v>
-      </c>
-      <c r="I7" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-2.84</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>060258364606</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sistema grifo</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>93</v>
-      </c>
-      <c r="E8" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>25.98</v>
-      </c>
-      <c r="I8" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>060258508031</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Brita Hub Filter 6/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>156</v>
-      </c>
-      <c r="E9" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="I9" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>060258364545</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Filtro botella</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>136</v>
-      </c>
-      <c r="E10" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>12.66</v>
-      </c>
-      <c r="I10" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>060258355031</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>109</v>
-      </c>
-      <c r="E11" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="I11" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>-21</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>060258363159</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>40</v>
-      </c>
-      <c r="E12" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="F12" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="I12" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>060258362442</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Filtro pitcher</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E13" t="n">
-        <v>28.88</v>
-      </c>
-      <c r="F13" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>20.56</v>
-      </c>
-      <c r="I13" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - fuerte</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>060258506884</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Pitcher</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>24</v>
-      </c>
-      <c r="E14" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="F14" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14</v>
-      </c>
-      <c r="H14" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>MARKETPLACE - marginal</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/brita_analisis_DWI.xlsx
+++ b/brita_analisis_DWI.xlsx
@@ -7,27 +7,30 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SAVVY vs DWI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Savvy vs DWI sensib" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Savvy vs DWI detalle" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="RESULTADO FINAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Resumen" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Por UPC (consolidado)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Detalle 73 lineas" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Alertas datos" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Para buscar en eBay" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Resumen por categoria" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Clasificacion Savvy" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Canal MARKETPLACE" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Canal PALLET" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Notas y escenarios" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Lotes pallet" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Pallet detalle" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Precios eBay" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Tarifas envio" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Sensibilidad envio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="LISTA OPERATIVA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SAVVY vs DWI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Savvy vs DWI sensib" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Savvy vs DWI detalle" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RESULTADO FINAL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resumen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Por UPC (consolidado)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Detalle 73 lineas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Alertas datos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Para buscar en eBay" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Resumen por categoria" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Clasificacion Savvy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Canal MARKETPLACE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Canal PALLET" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Notas y escenarios" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Lotes pallet" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Pallet detalle" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Precios eBay" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Tarifas envio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Sensibilidad envio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LISTA OPERATIVA'!$A$1:$N$46</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +49,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +86,16 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -92,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +121,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,411 +498,3450 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>CANAL</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Costo/und</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Precio venta</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>Utilidad/und</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Utilidad total</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Retail (MSRP)</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t># cont</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>Contenedores</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>Confianza precio</t>
+        </is>
+      </c>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>14220.06</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>E00408AA5FD1, E00408AFB2E5, E00408B0B552, E00408B208FE, E00408B3F881, E00408B3F8C3, E00408B3F8D7, E00408BD9111, E00408BF5C92, E00408C0CBE6, E00408C43D2F, E00408DA718F</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>060258362435</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>432</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1166.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4, E00408D5A73D</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>060258364606</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I4" t="n">
+        <v>635.1900000000001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4, E00408C0CBE6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>060258508031</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I5" t="n">
+        <v>566.28</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>E00408A25094</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="I6" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>060258363159</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="I7" t="n">
+        <v>282.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>060258363128</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I8" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="I9" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>E00408A25094</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>SAVVY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G10" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>E00408A25094</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1379.04</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>E004089FDE32, E00408A25094</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>524</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1252.36</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>E00408C0CBE6, E00408D25B54</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>AL FILO: los dos canales pagan casi igual, manda donde haya capacidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>140</v>
+      </c>
+      <c r="F13" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I13" t="n">
+        <v>995.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4, E00408C0CBE6, E00408C38DCB</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>CONFIRMAR pack size con vendedor (E00408C38DCB): 2 o 8 por caja. Swing $4,863. | Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>283</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I14" t="n">
+        <v>834.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>E00408B78418, E00408BD90EB, E00408C768A9, E00408D25B54</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>98</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I15" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="J15" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>E00408CA9696, E00408CAA556</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>060258365153</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>96</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I16" t="n">
+        <v>293.76</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>E00408DA7035</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>93</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>240.87</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>E00408D0A194</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>88</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I18" t="n">
+        <v>238.48</v>
+      </c>
+      <c r="J18" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>E00408B1FC60</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>060258506846</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>E004089EE70A</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>060258507010</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>96</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I20" t="n">
+        <v>226.56</v>
+      </c>
+      <c r="J20" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>E00408BB0E96</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>060258507447</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>144</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I21" t="n">
+        <v>204.48</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>E00408D1901D</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Filtro botella</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>136</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I22" t="n">
+        <v>187.68</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>E00408C0CBE6</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N22" s="13" t="inlineStr">
+        <is>
+          <t>AL FILO: los dos canales pagan casi igual, manda donde haya capacidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Filtro pitcher</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>109</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I23" t="n">
+        <v>167.86</v>
+      </c>
+      <c r="J23" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>E00408A25094, E00408B7F9F4, E00408C0CBE6</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>060258365252</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>48</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I24" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="J24" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>E00408A25094</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G25" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I25" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="J25" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>52</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I26" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>E00408A25094, E00408B13045, E00408B7F9F4, E00408C0CBE6</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>16</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I27" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="J27" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>060258509885</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>28</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>42</v>
+      </c>
+      <c r="J28" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N28" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>060258360936</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I29" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="J29" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>E00408A25094, E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>060258508956</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>91.17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="I30" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="J30" t="n">
+        <v>182.34</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>060258365245</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>18</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I31" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="J31" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="J32" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N32" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I33" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="J33" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>E00408A25094</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Botella</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="J34" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N34" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Filtro grifo</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="J35" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>E00408A25094</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N35" s="13" t="inlineStr">
+        <is>
+          <t>Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="J36" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N36" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G37" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="J37" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N37" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G38" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="J38" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N38" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="G39" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N39" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J40" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>E00408B7F9F4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N40" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pitcher</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="G41" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J41" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N41" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G42" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J42" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>E00408CAA556</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N42" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sistema grifo</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J43" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>E00408A25094</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ALTA - UPC exacto</t>
+        </is>
+      </c>
+      <c r="N43" s="13" t="inlineStr">
+        <is>
+          <t>Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J44" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N44" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>DWI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Dispenser</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J45" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>E00408BB3BB1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>MEDIA - por nombre (mismo tipo, no modelo exacto)</t>
+        </is>
+      </c>
+      <c r="N45" s="13" t="inlineStr">
+        <is>
+          <t>Precio de referencia por nombre, no del modelo exacto. | Cola larga: no listar solo, va en caja revuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr"/>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>44 SKUs (9 Savvy + 35 DWI)</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="n">
+        <v>7053</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="n">
+        <v>24401.74</v>
+      </c>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N46"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Canal</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SKUs</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>% SKUs</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Unidades</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>% unidades</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Costo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>% costo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Neto</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ROI</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UPC (12 dig)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Und_retail</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Costo/und</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>SAVVY (retail por unidad)</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>2860</v>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>$39,339</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>$17,253</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>060258359916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2082</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15.71</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>DWI (lote mas barato)</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>4193</v>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>$30,107</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>$7,148</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>060258355017</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.76</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>7053</v>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>$69,446</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>$24,402</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>060258356182</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>524</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.57</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>060258364552</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>140</v>
+      </c>
+      <c r="D5" t="n">
+        <v>32.17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>060258509670</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>283</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.78</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Concepto</t>
+          <t>060258362435</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Detalle</t>
-        </is>
+          <t>Brita Elite 12/1ct Sidekick Display</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>432</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.87</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>LA REGLA</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="n"/>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="1" t="n"/>
-      <c r="I8" s="1" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>060258507263</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14.92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Savvy $/und</t>
+          <t>060258365153</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>precio eBay conservador x (1 - 13.25% comision) - envio - costo</t>
-        </is>
+          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>96</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DWI $/und</t>
+          <t>060258364606</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50% del retail - costo (sin envio individual, va en tarima)</t>
-        </is>
+          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>93</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cada SKU va</t>
+          <t>060258508031</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>al canal que paga mas. La columna "Ventaja/und" dice cuanto gana Savvy sobre DWI (negativo = gana DWI).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Brita Hub Filter 6/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>156</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>060258509878</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>93</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11.75</v>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LA RESPUESTA CORTA</t>
-        </is>
+          <t>060258507492</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>88</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Para Savvy</t>
+          <t>060258506846</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9 SKUs de 44 (20%), pero son 57% del dinero y 71% de la utilidad</t>
-        </is>
+          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>96</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Para DWI</t>
+          <t>060258507010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>35 SKUs de 44 (80%), 43% del dinero y 29% de la utilidad</t>
-        </is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>96</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Por que</t>
+          <t>060258507447</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Savvy solo gana donde el producto es chico y ligero: filtros y sistemas de grifo. Todo lo voluminoso (pitchers, dispensers, botellas) lo gana DWI porque en lote no paga envio individual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>144</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060258364545</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>136</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.48</v>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EL SKU QUE MANDA</t>
-        </is>
+          <t>060258355031</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>109</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>060258359916 Filtros 10-pack</t>
+          <t>060258363159</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2,082 und -&gt; $14,220 de utilidad = 58% del total de la carga. Va a SAVVY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>40</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>060258362442</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>40</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11.84</v>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CASOS AL FILO</t>
-        </is>
+          <t>060258360899</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>52</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>060258356182 On Tap Chrome</t>
+          <t>060258365252</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>524 und. Savvy $2.18 vs DWI $2.39 - diferencia de 21 centavos. Cualquiera de los dos sirve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>48</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>060258506884</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13.41</v>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SUPUESTOS</t>
-        </is>
+          <t>060258506891</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DWI al 50% del retail</t>
+          <t>060258509885</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Es el default de tu Savvy Scanner. Si DWI vende a otro precio el reparto cambia - ver pestana "Savvy vs DWI sensib".</t>
-        </is>
+          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>28</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Comision eBay</t>
+          <t>060258508956</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13.25%</t>
-        </is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Envio</t>
+          <t>060258360936</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aproximado, validado por Octavio</t>
-        </is>
+          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>23</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Precios eBay</t>
+          <t>060258365245</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Listados activos, no ventas cerradas</t>
-        </is>
+          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>18</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>060258363128</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
+          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>11</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9.359999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060258364668</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060258363104</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060258364590</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>13.66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>060258364521</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8.359999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>060258363098</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>060258362619</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>060258507041</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>13.74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>060258507508</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23.68</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>060258509854</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>060258364170</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>060258507027</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13.74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>060258509724</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>060258509410</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>060258509847</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>060258507928</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>060258352146</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5.73</v>
       </c>
     </row>
   </sheetData>
@@ -881,7 +3949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1103,7 +4171,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3029,7 +6097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3717,7 +6785,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5233,7 +8301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5390,7 +8458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5586,7 +8654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6706,7 +9774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9624,7 +12692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9810,7 +12878,419 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SKUs</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>% SKUs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>% unidades</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>% costo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>SAVVY (retail por unidad)</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>2860</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>$39,339</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>$17,253</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>DWI (lote mas barato)</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>4193</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>$30,107</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>$7,148</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7053</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>$69,446</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>$24,402</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>LA REGLA</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="1" t="n"/>
+      <c r="I8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Savvy $/und</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>precio eBay conservador x (1 - 13.25% comision) - envio - costo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DWI $/und</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>50% del retail - costo (sin envio individual, va en tarima)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cada SKU va</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>al canal que paga mas. La columna "Ventaja/und" dice cuanto gana Savvy sobre DWI (negativo = gana DWI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LA RESPUESTA CORTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Para Savvy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9 SKUs de 44 (20%), pero son 57% del dinero y 71% de la utilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Para DWI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>35 SKUs de 44 (80%), 43% del dinero y 29% de la utilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Por que</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Savvy solo gana donde el producto es chico y ligero: filtros y sistemas de grifo. Todo lo voluminoso (pitchers, dispensers, botellas) lo gana DWI porque en lote no paga envio individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EL SKU QUE MANDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>060258359916 Filtros 10-pack</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2,082 und -&gt; $14,220 de utilidad = 58% del total de la carga. Va a SAVVY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CASOS AL FILO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>060258356182 On Tap Chrome</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>524 und. Savvy $2.18 vs DWI $2.39 - diferencia de 21 centavos. Cualquiera de los dos sirve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SUPUESTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DWI al 50% del retail</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Es el default de tu Savvy Scanner. Si DWI vende a otro precio el reparto cambia - ver pestana "Savvy vs DWI sensib".</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Comision eBay</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Envio</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aproximado, validado por Octavio</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Precios eBay</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Listados activos, no ventas cerradas</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9972,7 +13452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10155,7 +13635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12997,7 +16477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13290,7 +16770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13442,7 +16922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15234,7 +18714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19159,7 +22639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19339,838 +22819,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>UPC (12 dig)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Und_retail</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Costo/und</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>060258359916</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 10/10CT VALUE PALLET</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2082</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15.71</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>060258355017</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTERS 12/1CT</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2028</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>060258356182</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome 4/1ct</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>524</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9.57</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>060258364552</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brita SOHO Pitcher White w/Elite Filter 2/1ct</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>140</v>
-      </c>
-      <c r="D5" t="n">
-        <v>32.17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>060258509670</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Brita Champlain Pitcher Bright White 100/1ct Value Pallet</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>283</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11.78</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>060258362435</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Brita Elite 12/1ct Sidekick Display</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>432</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>060258507263</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Brita Wave Pitcher White 2ct Elite 54/1ct Value Pallet PK01</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>98</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14.92</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>060258365153</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BRITA PACIFICA PITCHER WHITE W/LONGLAST FILTER 2/1CT</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>96</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>060258364606</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Brita On Tap Filtration System Chrome/Chrome w/Extra Filter 4/1ct</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>93</v>
-      </c>
-      <c r="D10" t="n">
-        <v>13.54</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>060258508031</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Brita Hub Filter 6/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>156</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7.82</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>060258509878</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Brita Plus Everyday Pitcher - Clear 10 Cup</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>93</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>060258507492</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BRITA ULTRAMAX DISPENSER GRAY 1/1CT SIOC</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>88</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12.32</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>060258506846</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BRITA TAHOE PITCHER BRIGHT WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>96</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.98</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>060258507010</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator Teal 1/1ct</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>96</v>
-      </c>
-      <c r="D15" t="n">
-        <v>10.73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>060258507447</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Brita Metro Pitcher White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>144</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6.46</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>060258364545</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Brita Bottle Replacement Filters Hard Sided 8/6ct</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>136</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5.48</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>060258355031</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BRITA PITCHER FILTERS 24/3CT SHIPPER</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>109</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.19</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>060258363159</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 8/8CT</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>40</v>
-      </c>
-      <c r="D19" t="n">
-        <v>13.32</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>060258362442</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Brita Elite Pitcher Filters 8/2ct FM01</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>40</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11.84</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>060258360899</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER WHITE 2/1CT</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>52</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6.57</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>060258365252</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BRITA PREMIUM FILTERING BOTTLE HARD SIDED BLUSH 36OZ 6/1CT</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>48</v>
-      </c>
-      <c r="D22" t="n">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>060258506884</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite+ Filter Bright White 2/1ct</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>24</v>
-      </c>
-      <c r="D23" t="n">
-        <v>13.41</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>060258506891</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher w/ Elite Filter Black 2/1ct</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" t="n">
-        <v>13.74</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>060258509885</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Brita Plus Metro Pitcher - Stone Blue 6 Cup</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>28</v>
-      </c>
-      <c r="D25" t="n">
-        <v>6.81</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>060258508956</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Refillable Filter SIOC 1ct</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>74.76000000000001</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>060258360936</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BRITA SOHO PITCHER COLOR1 2/1CT</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>23</v>
-      </c>
-      <c r="D27" t="n">
-        <v>6.46</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>060258365245</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Sea Glass 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>18</v>
-      </c>
-      <c r="D28" t="n">
-        <v>6.97</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>060258363128</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Brita On Tap Replacement Filters Chrome 4/2ct 1 Tray</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" t="n">
-        <v>9.359999999999999</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>060258364668</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Hard Sided Orchid 36oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>12</v>
-      </c>
-      <c r="D30" t="n">
-        <v>6.97</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>060258363104</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS CHROME 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>12</v>
-      </c>
-      <c r="D31" t="n">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>060258364590</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP FILTRATION SYSTEM WHITE/WHITE W/EXTRA FILTER 4/1CT</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>13.66</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>060258364521</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Brita Premium Filtering Bottle Stainless Rose 20oz 6/1ct</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>6</v>
-      </c>
-      <c r="D33" t="n">
-        <v>8.359999999999999</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>060258363098</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BRITA ON TAP REPLACEMENT FILTERS WHITE 6/1CT 1 TRAY</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>6</v>
-      </c>
-      <c r="D34" t="n">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>060258362619</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Jet Black with Elite Filter 2/1ct PK05</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>060258507041</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher W/Smart Light Indicator w/LongLast+ Filter Mazarine Blue 1/1ct</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>13.74</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>060258507508</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Black 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>23.68</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>060258509854</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Brita Tahoe Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>10.47</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>060258364170</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BRITA ADVANCED PITCHER FILTER 2/6CT</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>10.43</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>060258507027</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Brita Everyday Pitcher w/ Smart Light Indicator w/ Elite+ Filter BrightBright White 1/1ct</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>13.74</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>060258509724</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Brita Plus White SIOC 1/1ct</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>060258509410</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Brita Ultramax Dispenser Translucent Jet Black w/ Brita Plus 1/1ct SIOC</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>060258509847</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Brita Denali Pitcher Stone Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>060258507928</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Brita UltraMax Dispenser Mazarine Blue 2/1ct</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
-        <v>11.55</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>060258352146</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>BRITA BASE FAUCET FILTRATION SYSTEM WHITE 4/1CT</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" t="n">
-        <v>5.73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>